--- a/dama/cases/营收系统数据标准/2 服务类/2.4 业务交易数据/2.4.2 收费信息/17. 实时收费交易日志.xlsx
+++ b/dama/cases/营收系统数据标准/2 服务类/2.4 业务交易数据/2.4.2 收费信息/17. 实时收费交易日志.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="175">
   <si>
     <t>业务属性</t>
   </si>
@@ -217,94 +217,97 @@
     <t>记录编号</t>
   </si>
   <si>
+    <t>PSB_RT_ID</t>
+  </si>
+  <si>
+    <t>营业收费系统</t>
+  </si>
+  <si>
+    <t>服务类</t>
+  </si>
+  <si>
+    <t>业务交易数据</t>
+  </si>
+  <si>
+    <t>收费信息</t>
+  </si>
+  <si>
+    <t>收费记录的主键唯一标识。</t>
+  </si>
+  <si>
+    <t>系统生成，唯一不可重复，非空。</t>
+  </si>
+  <si>
+    <t>供排水经营管理部</t>
+  </si>
+  <si>
+    <t>信息和网络安全管理中心</t>
+  </si>
+  <si>
+    <t>NUMBER</t>
+  </si>
+  <si>
+    <t>数值</t>
+  </si>
+  <si>
+    <t>数据库在线归档</t>
+  </si>
+  <si>
+    <t>满足归档条件自动归档</t>
+  </si>
+  <si>
+    <t>不可销毁</t>
+  </si>
+  <si>
+    <t>不执行销毁，仅通过业务状态标记停用</t>
+  </si>
+  <si>
+    <t>仅允许数字</t>
+  </si>
+  <si>
+    <t>唯一编码</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>低</t>
+  </si>
+  <si>
+    <t>一般业务数据</t>
+  </si>
+  <si>
+    <t>RCM_PSUBTOTAL_ID</t>
+  </si>
+  <si>
+    <t>收费小计编号</t>
+  </si>
+  <si>
+    <t>SUBTOTAL_ID</t>
+  </si>
+  <si>
+    <t>收费小计的主键唯一标识。</t>
+  </si>
+  <si>
+    <t>RCM_PTOTAL_ID</t>
+  </si>
+  <si>
+    <t>收费汇总编号</t>
+  </si>
+  <si>
+    <t>TOTAL_ID</t>
+  </si>
+  <si>
+    <t>收费汇总的主键唯一标识。</t>
+  </si>
+  <si>
+    <t>RCM_RT_ID</t>
+  </si>
+  <si>
+    <t>代收机构代码</t>
+  </si>
+  <si>
     <t>RT_ID</t>
-  </si>
-  <si>
-    <t>营业收费系统</t>
-  </si>
-  <si>
-    <t>服务类</t>
-  </si>
-  <si>
-    <t>业务交易数据</t>
-  </si>
-  <si>
-    <t>收费信息</t>
-  </si>
-  <si>
-    <t>收费记录的主键唯一标识。</t>
-  </si>
-  <si>
-    <t>系统生成，唯一不可重复，非空。</t>
-  </si>
-  <si>
-    <t>供排水经营管理部</t>
-  </si>
-  <si>
-    <t>信息和网络安全管理中心</t>
-  </si>
-  <si>
-    <t>NUMBER</t>
-  </si>
-  <si>
-    <t>数值</t>
-  </si>
-  <si>
-    <t>数据库在线归档</t>
-  </si>
-  <si>
-    <t>满足归档条件自动归档</t>
-  </si>
-  <si>
-    <t>不可销毁</t>
-  </si>
-  <si>
-    <t>不执行销毁，仅通过业务状态标记停用</t>
-  </si>
-  <si>
-    <t>仅允许数字</t>
-  </si>
-  <si>
-    <t>唯一编码</t>
-  </si>
-  <si>
-    <t>是</t>
-  </si>
-  <si>
-    <t>低</t>
-  </si>
-  <si>
-    <t>一般业务数据</t>
-  </si>
-  <si>
-    <t>RCM_PSUBTOTAL_ID</t>
-  </si>
-  <si>
-    <t>收费小计编号</t>
-  </si>
-  <si>
-    <t>SUBTOTAL_ID</t>
-  </si>
-  <si>
-    <t>收费小计的主键唯一标识。</t>
-  </si>
-  <si>
-    <t>RCM_PTOTAL_ID</t>
-  </si>
-  <si>
-    <t>收费汇总编号</t>
-  </si>
-  <si>
-    <t>TOTAL_ID</t>
-  </si>
-  <si>
-    <t>收费汇总的主键唯一标识。</t>
-  </si>
-  <si>
-    <t>RCM_RT_ID</t>
-  </si>
-  <si>
-    <t>代收机构代码</t>
   </si>
   <si>
     <t>代收机构的业务标识编码。</t>
@@ -548,7 +551,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -581,13 +584,6 @@
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1076,48 +1072,51 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1127,97 +1126,94 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2090,7 +2086,7 @@
         <v>96</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>68</v>
@@ -2105,10 +2101,10 @@
         <v>71</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
@@ -2123,10 +2119,10 @@
         <v>75</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R7" s="10">
         <v>50</v>
@@ -2147,10 +2143,10 @@
       </c>
       <c r="Y7" s="8"/>
       <c r="Z7" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AA7" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AB7" s="7" t="s">
         <v>84</v>
@@ -2164,13 +2160,13 @@
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:30">
       <c r="A8" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>68</v>
@@ -2185,10 +2181,10 @@
         <v>71</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -2203,10 +2199,10 @@
         <v>75</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R8" s="9">
         <v>50</v>
@@ -2227,10 +2223,10 @@
       </c>
       <c r="Y8" s="6"/>
       <c r="Z8" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AA8" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AB8" s="5" t="s">
         <v>84</v>
@@ -2244,13 +2240,13 @@
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:30">
       <c r="A9" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>68</v>
@@ -2265,10 +2261,10 @@
         <v>71</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
@@ -2312,7 +2308,7 @@
         <v>82</v>
       </c>
       <c r="AA9" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AB9" s="7" t="s">
         <v>84</v>
@@ -2326,13 +2322,13 @@
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:30">
       <c r="A10" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>68</v>
@@ -2347,10 +2343,10 @@
         <v>71</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
@@ -2365,10 +2361,10 @@
         <v>75</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="R10" s="9">
         <v>7</v>
@@ -2389,10 +2385,10 @@
       </c>
       <c r="Y10" s="6"/>
       <c r="Z10" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AA10" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AB10" s="5" t="s">
         <v>84</v>
@@ -2406,13 +2402,13 @@
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:30">
       <c r="A11" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>68</v>
@@ -2427,10 +2423,10 @@
         <v>71</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
@@ -2445,10 +2441,10 @@
         <v>75</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R11" s="10">
         <v>4000</v>
@@ -2469,10 +2465,10 @@
       </c>
       <c r="Y11" s="8"/>
       <c r="Z11" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AB11" s="7" t="s">
         <v>84</v>
@@ -2486,13 +2482,13 @@
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:30">
       <c r="A12" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>68</v>
@@ -2507,10 +2503,10 @@
         <v>71</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
@@ -2537,7 +2533,7 @@
         <v>2</v>
       </c>
       <c r="T12" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="U12" s="6" t="s">
         <v>78</v>
@@ -2556,7 +2552,7 @@
         <v>82</v>
       </c>
       <c r="AA12" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AB12" s="5" t="s">
         <v>84</v>
@@ -2570,13 +2566,13 @@
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:30">
       <c r="A13" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>68</v>
@@ -2591,10 +2587,10 @@
         <v>71</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
@@ -2621,7 +2617,7 @@
         <v>2</v>
       </c>
       <c r="T13" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="U13" s="8" t="s">
         <v>78</v>
@@ -2640,7 +2636,7 @@
         <v>82</v>
       </c>
       <c r="AA13" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AB13" s="7" t="s">
         <v>84</v>
@@ -2654,13 +2650,13 @@
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:30">
       <c r="A14" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>68</v>
@@ -2675,10 +2671,10 @@
         <v>71</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
@@ -2693,10 +2689,10 @@
         <v>75</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R14" s="9">
         <v>120</v>
@@ -2717,30 +2713,30 @@
       </c>
       <c r="Y14" s="6"/>
       <c r="Z14" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AA14" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AB14" s="5" t="s">
         <v>84</v>
       </c>
       <c r="AC14" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AD14" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:30">
       <c r="A15" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>68</v>
@@ -2755,10 +2751,10 @@
         <v>71</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
@@ -2773,10 +2769,10 @@
         <v>75</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R15" s="10">
         <v>120</v>
@@ -2797,10 +2793,10 @@
       </c>
       <c r="Y15" s="8"/>
       <c r="Z15" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AA15" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AB15" s="7" t="s">
         <v>84</v>
@@ -2814,13 +2810,13 @@
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:30">
       <c r="A16" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>68</v>
@@ -2835,10 +2831,10 @@
         <v>71</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -2882,7 +2878,7 @@
         <v>82</v>
       </c>
       <c r="AA16" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AB16" s="5" t="s">
         <v>84</v>
@@ -2896,13 +2892,13 @@
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:30">
       <c r="A17" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>68</v>
@@ -2917,10 +2913,10 @@
         <v>71</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
@@ -2964,10 +2960,10 @@
         <v>82</v>
       </c>
       <c r="AA17" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AB17" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AC17" s="7" t="s">
         <v>85</v>
@@ -2978,13 +2974,13 @@
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:30">
       <c r="A18" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>68</v>
@@ -2999,10 +2995,10 @@
         <v>71</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
@@ -3027,7 +3023,7 @@
       </c>
       <c r="S18" s="9"/>
       <c r="T18" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="U18" s="6" t="s">
         <v>78</v>
@@ -3046,7 +3042,7 @@
         <v>82</v>
       </c>
       <c r="AA18" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AB18" s="5" t="s">
         <v>84</v>
